--- a/Lab_4/data/partB/param_optimization_process/v100_k20_s200_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v100_k20_s200_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
         <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -573,19 +573,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -606,13 +606,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
         <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -652,13 +652,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -677,28 +677,28 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
         <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -707,16 +707,16 @@
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -729,46 +729,46 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -787,25 +787,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>53</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>51</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -814,13 +814,13 @@
         <v>7</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -842,34 +842,34 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>12</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
@@ -882,49 +882,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -937,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -958,25 +958,25 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
         <v>13</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
         <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
         <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1090,46 +1090,46 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
         <v>5</v>
       </c>
-      <c r="G13" t="n">
-        <v>6</v>
-      </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1142,49 +1142,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1200,10 +1200,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1249,37 +1249,37 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
         <v>3</v>
@@ -1288,7 +1288,7 @@
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18335,7 +18335,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22228,7 +22228,7 @@
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24438,7 +24438,7 @@
       </c>
       <c r="C1361" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="C1362" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26223,7 +26223,7 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26461,7 +26461,7 @@
       </c>
       <c r="C1480" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
